--- a/testCases.xlsx
+++ b/testCases.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/0466ad851ab465d0/ドキュメント/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="179" documentId="8_{78DD7B1F-C25B-488F-AEEB-509655B3A9D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{86B7D72B-A1EB-4982-82DB-8CEEBE73C91F}"/>
+  <xr:revisionPtr revIDLastSave="182" documentId="8_{78DD7B1F-C25B-488F-AEEB-509655B3A9D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8A50114C-9FE1-4A17-BA6C-F445CA26B7F9}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Traditional" sheetId="1" r:id="rId1"/>
@@ -318,9 +318,6 @@
     <t>Users add invalid email, subject and body</t>
   </si>
   <si>
-    <t>Clicks on the send button, invalid email messgae has to be sent back to user</t>
-  </si>
-  <si>
     <t>Logged in and cliked on compose</t>
   </si>
   <si>
@@ -328,14 +325,19 @@
 doesn’t click on the send button</t>
   </si>
   <si>
-    <t>Email has to be available in the Draft tab and user shall be able to edit it</t>
-  </si>
-  <si>
     <t>Available in draft</t>
   </si>
   <si>
     <t>Logged in and clicked onCompose
 button</t>
+  </si>
+  <si>
+    <t>Clicks on the send button, invalid 
+email messgae has to be sent back to user</t>
+  </si>
+  <si>
+    <t>Email has to be available in the 
+Draft tab and user shall be able to edit it</t>
   </si>
 </sst>
 </file>
@@ -370,7 +372,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -378,11 +380,26 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -394,6 +411,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -409,6 +428,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -684,23 +707,23 @@
     <col min="5" max="5" width="40.7265625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:6" s="6" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="5" t="s">
         <v>5</v>
       </c>
     </row>
@@ -1046,7 +1069,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:5" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A6" s="4" t="s">
         <v>72</v>
       </c>
@@ -1054,13 +1077,13 @@
         <v>90</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D6" s="4" t="s">
         <v>91</v>
       </c>
-      <c r="E6" s="4" t="s">
-        <v>92</v>
+      <c r="E6" s="3" t="s">
+        <v>96</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="43.5" x14ac:dyDescent="0.35">
@@ -1068,16 +1091,16 @@
         <v>73</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="C7" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="E7" s="3" t="s">
         <v>97</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="E7" s="4" t="s">
-        <v>95</v>
       </c>
     </row>
   </sheetData>
